--- a/internal_doc/05.测试设计/参数校验/测试用例/集群管理（CM管理）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/集群管理（CM管理）参数校验测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="136">
   <si>
     <t>name</t>
   </si>
@@ -502,19 +502,71 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>a.执行service sdbcm start启动停止状态的CM，启动成功，执行service sdbcm status查看状态为running状态；
+b.执行service sdbcm stop 停止启动状态的CM，停止成功，执行service sdbcm status查看状态为not running ...状态；
+c.执行service sdbcm status 查看CM状态,CM状态与实际CM状态一致；
+d.执行service sdbcm restart 重启CM，重启成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、在sdbcm.conf该配置文件中找不到对应主机的参数，sdbcm 会以 defaultPort 启动
+2、CM启动成功，执行service sdbcm status查看状态为running状态；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、若在该配置文件中找不到对应主机的参数，sdbcm 会以 defaultPort 启动；若 defaultPort 也不存在，则 sdbcm 以默认端口11790启动。
+2、CM启动成功，执行service sdbcm status查看状态为running状态；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，CM服务端口为11790，配置sdbcm.conf，配置如下：
+&lt;hostname&gt;_Port参数不存在
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，&lt;hostname&gt;_Port端口和defaultPort参数不存在，且实际的端口不是11790</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，CM服务端口非11790，配置sdbcm.conf，配置如下：
+&lt;hostname&gt;_Port端口错误
+defaultPort参数不存在
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CM启动失败，sdbcm.conf日志打印CM端口错误，打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CM启动失败，sdbcm.conf日志打印主机不存在，打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，AutoStart参数非法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AutoStart:true|false，默认为true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中AutoStart参数正确，覆盖如下取值：
   a.配置AutoStart=TRUE
   b.配置AutoStart=FALSE
 其他参数配置正确
 2、执行reboot重启主机，查看CM是否自动拉起；
-3、重启后重启CM后查看sdbcm.log的参数跟配置的参数是否一致</t>
+3、查看sdbcm.log的参数跟配置的参数是否一致</t>
   </si>
   <si>
     <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中IsGeneral和OMAddress参数正确，覆盖如下取值：
   a.配置IsGeneral=TRUE 且OMAddress参数正确，如配置OMAddress=ubuntu:11785，其中主机名和端口跟实际OM一致
   b.配置IsGeneral=FALSE
 其他参数配置正确
-2、执行service sdbcm restart重启CM，重启后重启CM后查看sdbcm.log的参数跟配置的参数是否一致</t>
+2、执行service sdbcm restart重启CM，查看sdbcm.log的参数跟配置的参数是否一致</t>
   </si>
   <si>
     <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中DiagLevel参数正确，覆盖如下取值：
@@ -525,82 +577,333 @@
   b.配置DiagLevel=4
   b.配置DiagLevel=5
 其他参数配置正确
-2、执行service sdbcm restart重启CM，重启后重启CM后查看sdbcm.log的参数跟配置的参数是否一致
+2、执行service sdbcm restart重启CM，查看sdbcm.log的参数跟配置的参数是否一致
 3、查看sdbcm.log日志级别打印正确</t>
   </si>
   <si>
     <t>1、sdbadmin用户登录CM服务器，配置sdbcm.conf中RestartCount参数不存在
 2、执行service sdbcm restart重启CM使参数生效；模拟CM重启多次场景，如CM所在服务器断网，查看CM重启状态
-3、重启CM后查看sdbcm.log的参数跟配置的参数是否一致</t>
-  </si>
-  <si>
-    <t>1、sdbadmin用户登录CM服务器，配置sdbcm.conf中RestartCount=5，模拟CM重启多次场景，如CM所在服务器断网，查看CM重启状态
-2、重启CM后查看sdbcm.log的参数跟配置的参数是否一致</t>
+3、查看sdbcm.log的参数跟配置的参数是否一致</t>
   </si>
   <si>
     <t>1、sdbadmin用户登录CM服务器，配置sdbcm.conf中RestartInterval参数不存在
 2、执行service sdbcm restart重启CM使参数生效；模拟CM重启多次场景，如CM所在服务器断网，查看CM重启状态
-3、重启CM后查看sdbcm.log的参数跟配置的参数是否一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+3、查看sdbcm.log的参数跟配置的参数是否一致</t>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，配置sdbcm.conf中RestartCount=5，模拟CM重启多次场景，如CM所在服务器断网，查看CM重启状态
+2、查看sdbcm.log的参数跟配置的参数是否一致</t>
   </si>
   <si>
     <t>1、sdbadmin用户登录CM服务器，配置sdbcm.conf，配置如下：
 &lt;hostname&gt;_Port端口不存在
 defaultPort配置正确
 其他参数配置正确
-2、执行service sdbcm restart重启CM使参数生效，重启CM后查看sdbcm.log的参数跟配置的参数是否一致，查看重启结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>a.执行service sdbcm start启动停止状态的CM，启动成功，执行service sdbcm status查看状态为running状态；
-b.执行service sdbcm stop 停止启动状态的CM，停止成功，执行service sdbcm status查看状态为not running ...状态；
-c.执行service sdbcm status 查看CM状态,CM状态与实际CM状态一致；
-d.执行service sdbcm restart 重启CM，重启成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、在sdbcm.conf该配置文件中找不到对应主机的参数，sdbcm 会以 defaultPort 启动
-2、CM启动成功，执行service sdbcm status查看状态为running状态；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、若在该配置文件中找不到对应主机的参数，sdbcm 会以 defaultPort 启动；若 defaultPort 也不存在，则 sdbcm 以默认端口11790启动。
-2、CM启动成功，执行service sdbcm status查看状态为running状态；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+2、执行service sdbcm restart重启CM使参数生效，查看sdbcm.log的参数跟配置的参数是否一致，查看重启结果</t>
   </si>
   <si>
     <t>1、sdbadmin用户登录CM服务器，CM服务端口为11790，配置sdbcm.conf，配置如下：
 &lt;hostname&gt;_Port端口不存在
 defaultPort参数不存在
 其他参数配置正确
-2、执行service sdbcm restart重启CM使参数生效，重启CM后查看sdbcm.log的参数跟配置的参数是否一致，查看重启结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdbadmin用户登录CM服务器，CM服务端口为11790，配置sdbcm.conf，配置如下：
-&lt;hostname&gt;_Port参数不存在
-其他参数配置正确
-2、执行service sdbcm restart重启CM，检查重启结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdbcm.conf，&lt;hostname&gt;_Port端口和defaultPort参数不存在，且实际的端口不是11790</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdbadmin用户登录CM服务器，CM服务端口非11790，配置sdbcm.conf，配置如下：
-&lt;hostname&gt;_Port端口错误
-defaultPort参数不存在
-其他参数配置正确
-2、执行service sdbcm restart重启CM，检查重启结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CM启动失败，sdbcm.conf日志打印CM端口错误，打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CM启动失败，sdbcm.conf日志打印主机不存在，打印信息合理准确</t>
+2、执行service sdbcm restart重启CM使参数生效，查看sdbcm.log的参数跟配置的参数是否一致，查看重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中AutoStart参数非法，
+如：
+  配置AutoStart取值为：test*、-1、yes/no、y/n、T/F
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，AutoStart参数为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中AutoStart参数为空
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，AutoStart参数不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，DiagLevel参数非法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，DiagLevel参数为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，DiagLevel参数不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中DiagLevel参数非法，
+如：
+  配置DiagLevel取值为：-1、6、test@123
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重启失败，查看sdbcm.log文件提示sdbcm.conf参数配置错误，日志提示合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，IsGeneral参数非法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，IsGeneral参数为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，IsGeneral参数不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，OMAddress参数不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，OMAddress指定的地址非OM地址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重启失败，查看sdbcm.log文件提示OMAddress连通失败，日志提示合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中OMAddress指定的地址非OM地址，如ubuntu:11785没有安装OM，配置IsGeneral=true
+OMAddress=ubuntu:11785
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，OMAddress指定的主机名正确但端口错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中端口错误，如ubuntu-n13主机OM端口为8888，配置为ubuntu:7777，配置IsGeneral=true
+OMAddress=ubuntu:7777
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，OMAddress为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，RestartCount为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，RestartCount参数非法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，RestartInterval参数非法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，RestartInterval为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中IsGeneral参数非法，
+如：
+  配置IsGeneral取值为：test*、-1、yes/no
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中RestartCount参数非法，
+如：
+  配置RestartCount取值为：-2、test123*
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中RestartInterval参数非法，
+如：
+  配置RestartInterval取值为：-1、test123*
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，defaultPort参数非法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，defaultPort为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中defaultPort参数非法，
+如：
+  配置defaultPort取值为：test&amp;*1
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，&lt;hostname&gt;_Port参数非法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中&lt;hostname&gt;_Port参数非法，
+如：
+  配置&lt;hostname&gt;_Port取值为：test*_Port=11790
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，CM跟OM不在同一主机，配置DiagLevel/IsGeneral/OMAddress/&lt;hostname&gt;_Port参数正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，如下参数配置正确：
+AutoStart=TRUE
+DiagLevel=3
+IsGeneral=TRUE
+OMAddress=ubuntu-n13:11785
+RestartCount=5
+RestartInterval=0
+defaultPort=11790
+ubuntu-n13_Port=11790
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM跟OM在同一台主机，sdbcm.conf配置参数：
+AutoStart=TRUE
+DiagLevel=3
+IsGeneral=TRUE
+OMAddress=ubuntu-n13:11785
+RestartCount=5
+RestartInterval=0
+defaultPort=11790
+ubuntu-n13_Port=11790
+CM跟OM不在同一台主机，sdbcm.conf配置参数：AutoStart=TRUE
+RestartCount=5
+RestartInterval=0
+defaultPort=11790</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、重启成功，CM跟OM不在同一主机，CM只读如下几个参数，其他参数均忽略
+AutoStart=TRUE
+RestartCount=5
+RestartInterval=0
+defaultPort=11790
+2、查看sdbcm.log打印如上几个参数，参数值显示正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中AutoStart参数不存在
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中DiagLevel参数为空
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中DiagLevel参数不存在
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中IsGeneral参数为空
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中IsGeneral参数不存在
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中OMAddress参数为空
+  b.OMAddress参数不存在
+IsGeneral=true，其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中OMAddress参数不存在，
+IsGeneral=true，其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中RestartCount参数为空
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中RestartCount参数不存在
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中RestartInterval参数为空，
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中RestartInterval参数不存在
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm.conf，defaultPort参数不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中defaultPort参数为空，
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中defaultPort参数不存在
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中&lt;hostname&gt;_Port参数为空，
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录CM服务器，该CM与OM在同一台机器，配置sdbcm.conf中&lt;hostname&gt;_Port参数不存在
+其他参数配置正确
+2、执行service sdbcm restart重启CM，检查重启结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -659,7 +962,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -678,6 +981,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -768,8 +1074,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I26" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I47" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I47"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1088,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26.375" style="1" customWidth="1"/>
@@ -1258,7 +1564,7 @@
         <v>37</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -1330,7 +1636,7 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>51</v>
@@ -1351,7 +1657,7 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>50</v>
@@ -1387,14 +1693,14 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>55</v>
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" ht="94.5">
+    <row r="15" spans="1:9" ht="81">
       <c r="A15" s="1" t="s">
         <v>43</v>
       </c>
@@ -1408,7 +1714,7 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>56</v>
@@ -1429,7 +1735,7 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>59</v>
@@ -1449,7 +1755,7 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>61</v>
@@ -1470,10 +1776,10 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="I18" s="4"/>
     </row>
@@ -1485,82 +1791,409 @@
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="4"/>
+    </row>
+    <row r="20" spans="1:9" ht="108">
+      <c r="A20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="I19" s="4"/>
-    </row>
-    <row r="20" spans="1:9">
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
+      <c r="G20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>93</v>
+      </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" ht="67.5">
+      <c r="A21" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
+      <c r="G21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>93</v>
+      </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" ht="67.5">
+      <c r="A22" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>93</v>
+      </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" ht="94.5">
+      <c r="A23" s="1" t="s">
+        <v>89</v>
+      </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
+      <c r="G23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>93</v>
+      </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" ht="67.5">
+      <c r="A24" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
+      <c r="G24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>93</v>
+      </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="81">
+    <row r="25" spans="1:9" ht="67.5">
       <c r="A25" s="1" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>82</v>
+        <v>122</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="94.5">
       <c r="A26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
+        <v>94</v>
+      </c>
       <c r="G26" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I26" s="4"/>
+        <v>108</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="67.5">
+      <c r="A27" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="67.5">
+      <c r="A28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="108">
+      <c r="A29" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="108">
+      <c r="A30" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="81">
+      <c r="A31" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="67.5">
+      <c r="A32" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="94.5">
+      <c r="A33" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="G33" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="67.5">
+      <c r="A34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I34" s="4"/>
+    </row>
+    <row r="35" spans="1:9" ht="67.5">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I35" s="4"/>
+    </row>
+    <row r="36" spans="1:9" ht="108">
+      <c r="A36" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I36" s="4"/>
+    </row>
+    <row r="37" spans="1:9" ht="81">
+      <c r="A37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" spans="1:9" ht="81">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I38" s="4"/>
+    </row>
+    <row r="39" spans="1:9" ht="94.5">
+      <c r="A39" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I39" s="4"/>
+    </row>
+    <row r="40" spans="1:9" ht="67.5">
+      <c r="A40" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" spans="1:9" ht="67.5">
+      <c r="A41" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I41" s="4"/>
+    </row>
+    <row r="42" spans="1:9" ht="121.5">
+      <c r="A42" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I42" s="4"/>
+    </row>
+    <row r="43" spans="1:9" ht="81">
+      <c r="A43" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I43" s="4"/>
+    </row>
+    <row r="44" spans="1:9" ht="81">
+      <c r="A44" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I44" s="4"/>
+    </row>
+    <row r="45" spans="1:9" ht="81">
+      <c r="A45" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I45" s="4"/>
+    </row>
+    <row r="46" spans="1:9" ht="94.5">
+      <c r="A46" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I46" s="4"/>
+    </row>
+    <row r="47" spans="1:9" ht="229.5">
+      <c r="A47" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I47" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
